--- a/output.xlsx
+++ b/output.xlsx
@@ -644,7 +644,7 @@
     <row r="2" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>5F-15-R12</t>
+          <t>5F-31-R04</t>
         </is>
       </c>
       <c r="C2" s="9" t="n"/>
@@ -685,21 +685,9 @@
       <c r="B5" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>S5296</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>HPC NW 스위치#1 (25G 스위치)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B6" s="2" t="n">
@@ -721,29 +709,29 @@
       <c r="B8" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>S3148</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>HPC ILO SW #1 (1G 스위치)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B9" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>DL380 GEN10 Plus</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>대외 SFTP용 서버 운영 #2</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>신동민</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B10" s="2" t="n">
@@ -751,17 +739,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DS-6505B</t>
+          <t>DL380 GEN10 Plus</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>HPC SAN 스위치 #1</t>
+          <t>대외 SFTP용 서버 운영 #2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>신동민</t>
         </is>
       </c>
     </row>
@@ -777,17 +765,41 @@
       <c r="B12" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>DL380 GEN10</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>이미지 메인 WAS 운영 #1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>김진, 오재승</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B13" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>DL380 GEN10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>이미지 메인 WAS 운영 #1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>김진, 오재승</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B14" s="2" t="n">
@@ -801,9 +813,21 @@
       <c r="B15" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>DL380 GEN10</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>이미지 서브 WAS 운영 #1</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>김진, 오재승</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B16" s="2" t="n">
@@ -811,18 +835,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Unity 380F
-Unity 350F</t>
+          <t>DL380 GEN10</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>HPC 스토리지</t>
+          <t>이미지 서브 WAS 운영 #1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>김진, 오재승</t>
         </is>
       </c>
     </row>
@@ -838,9 +861,21 @@
       <c r="B18" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>DL380 GEN10</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>이미지 ECP AP 운영 #1</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>김진, 오재승</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B19" s="2" t="n">
@@ -848,17 +883,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>R740</t>
+          <t>DL380 GEN10</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>HPC 변액햇지 SQL DB #1</t>
+          <t>이미지 ECP AP 운영 #1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>이원섭</t>
+          <t>김진, 오재승</t>
         </is>
       </c>
     </row>
@@ -874,9 +909,21 @@
       <c r="B21" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>DL380 GEN10</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>이미지 DB 운영 #1</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>배수근</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B22" s="2" t="n">
@@ -884,17 +931,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>R740</t>
+          <t>DL380 GEN10</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>변액헷지 DB #1</t>
+          <t>이미지 DB 운영 #1</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>이원섭</t>
+          <t>배수근</t>
         </is>
       </c>
     </row>
@@ -926,37 +973,49 @@
       <c r="B26" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>DL380 GEN11</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>신규 SWIFT #1</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>박상수</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B27" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>DL380 GEN11</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>신규 SWIFT #1</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>박상수</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B28" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>R640</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>변액헷지 AD관리 서버 #1</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>이원섭</t>
-        </is>
-      </c>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B29" s="2" t="n">
@@ -964,17 +1023,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>R640</t>
+          <t>DL380 GEN11</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>HPC 관리노드 2 (변액헷지 관리#2)</t>
+          <t>비대면 인증 운영 DB #1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>이원섭</t>
+          <t>김누리</t>
         </is>
       </c>
     </row>
@@ -982,57 +1041,57 @@
       <c r="B30" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>DL380 GEN11</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>비대면 인증 운영 DB #1</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>김누리</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B31" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>R640</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>HPC 관리노드 1 (변액헷지 관리#1)</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>이원섭</t>
-        </is>
-      </c>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B32" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>R640</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>HPC 연산노드 #9</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>이원섭</t>
-        </is>
-      </c>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B33" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>DL380 GEN11</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>AICC 통합 DB #1</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>김누리</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B34" s="2" t="n">
@@ -1040,17 +1099,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>R640</t>
+          <t>DL380 GEN11</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>HPC 연산노드 #8</t>
+          <t>AICC 통합 DB #1</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>이원섭</t>
+          <t>김누리</t>
         </is>
       </c>
     </row>
@@ -1058,29 +1117,29 @@
       <c r="B35" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>R640</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>HPC 연산노드 #7</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>이원섭</t>
-        </is>
-      </c>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>DL580 GEN10</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>TSQL 고도화 서버#1 대고객서비스 운영 DB</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>오지윤</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B37" s="2" t="n">
@@ -1088,17 +1147,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>R640</t>
+          <t>DL580 GEN10</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>HPC 연산노드 #6</t>
+          <t>TSQL 고도화 서버#1 대고객서비스 운영 DB</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>이원섭</t>
+          <t>오지윤</t>
         </is>
       </c>
     </row>
@@ -1108,17 +1167,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>R640</t>
+          <t>DL580 GEN10</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>HPC 연산노드 #5</t>
+          <t>TSQL 고도화 서버#1 대고객서비스 운영 DB</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>이원섭</t>
+          <t>오지윤</t>
         </is>
       </c>
     </row>
@@ -1126,29 +1185,29 @@
       <c r="B39" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>DL580 GEN10</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>TSQL 고도화 서버#1 대고객서비스 운영 DB</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>오지윤</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B40" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>R640</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>HPC 연산노드 #4</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>이원섭</t>
-        </is>
-      </c>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B41" s="2" t="n">
@@ -1156,17 +1215,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>R640</t>
+          <t>DL580 GEN10</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>HPC 연산노드 #3</t>
+          <t>SSQL 고도화 서버#1 보안서비스 운영 DB</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>이원섭</t>
+          <t>이용준</t>
         </is>
       </c>
     </row>
@@ -1174,9 +1233,21 @@
       <c r="B42" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>DL580 GEN10</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>SSQL 고도화 서버#1 보안서비스 운영 DB</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>이용준</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="18" customHeight="1" s="7" thickBot="1">
       <c r="B43" s="2" t="n">
@@ -1184,17 +1255,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>R640</t>
+          <t>DL580 GEN10</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>HPC 연산노드 #2</t>
+          <t>SSQL 고도화 서버#1 보안서비스 운영 DB</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>이원섭</t>
+          <t>이용준</t>
         </is>
       </c>
     </row>
@@ -1204,17 +1275,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>R640</t>
+          <t>DL580 GEN10</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>HPC 연산노드 #1</t>
+          <t>SSQL 고도화 서버#1 보안서비스 운영 DB</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>이원섭</t>
+          <t>이용준</t>
         </is>
       </c>
     </row>
